--- a/zy72088/ml_threshold_calibrator/output/demo_results_latest.xlsx
+++ b/zy72088/ml_threshold_calibrator/output/demo_results_latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="63">
   <si>
     <t>指标名称</t>
   </si>
@@ -76,15 +76,24 @@
     <t>新用户7日留存</t>
   </si>
   <si>
+    <t>需人工确认</t>
+  </si>
+  <si>
+    <t>参数冲突待裁决</t>
+  </si>
+  <si>
     <t>顺利通过</t>
   </si>
   <si>
-    <t>参数冲突待裁决</t>
+    <t>历史口径补全</t>
   </si>
   <si>
     <t>样本越界</t>
   </si>
   <si>
+    <t>中</t>
+  </si>
+  <si>
     <t>高</t>
   </si>
   <si>
@@ -109,7 +118,7 @@
     <t>2023年底校准：大促后均值稳定在140-160区间</t>
   </si>
   <si>
-    <t>nan</t>
+    <t>2023年校准备忘：当时活动少复购偏低</t>
   </si>
   <si>
     <t>2024Q1技术优化后性能提升，从5秒下调到3秒</t>
@@ -121,7 +130,7 @@
     <t>运营说要调高但还没确认</t>
   </si>
   <si>
-    <t>样本分布正常，建议按P95分位校准但不低于当前阈值的95%。计算依据：样本P95=0.05, 当前阈值×0.95=0.05。这样既利用了新数据，又不会让阈值降太低。</t>
+    <t>有样本超出阈值但不严重，建议按样本P95分位校准。计算依据：样本P95=0.05，这个值能覆盖95%的正常情况。如果业务上希望更严格，可以保持当前阈值 0.05。</t>
   </si>
   <si>
     <t>存在参数冲突，需要您先确认哪边数据准确。建议：1) 核对两边数据来源；2) 确认业务口径是否变化；3) 在参数表中更新最终值。</t>
@@ -130,31 +139,43 @@
     <t>该指标之前人工调整过，为避免覆盖您的校准成果，本次保持原值。如需要重新计算，请先在参数表中移除'人工调整过'标记。</t>
   </si>
   <si>
-    <t>样本分布正常，建议按P95分位校准但不低于当前阈值的95%。计算依据：样本P95=0.26, 当前阈值×0.95=0.24。这样既利用了新数据，又不会让阈值降太低。</t>
+    <t>有样本超出阈值但不严重，建议按样本P95分位校准。计算依据：样本P95=159.00，这个值能覆盖95%的正常情况。如果业务上希望更严格，可以保持当前阈值 150.0。</t>
+  </si>
+  <si>
+    <t>从历史口径补全，参数表中无对应记录，沿用历史校准结果</t>
   </si>
   <si>
     <t>检测到越界样本，按99分位+阈值上浮20%的保守策略建议。计算依据：样本P99=5.17, 当前阈值×1.2=3.60, 取较大值。如果觉得太松，可以改为P95=5.06。</t>
   </si>
   <si>
-    <t>参数表与导入数据阈值冲突，请人工裁决</t>
-  </si>
-  <si>
-    <t>样本值 4.5 高于当前阈值 3.0; 样本值 5.2 超出当前阈值 3.0 的150%</t>
-  </si>
-  <si>
-    <t>样本值 0.025 超出当前阈值 0.015 的150%</t>
-  </si>
-  <si>
-    <t>{'样本数量': 5, '样本均值': 0.05, 'P95分位': 0.05, 'P99分位': 0.05}</t>
+    <t>样本值 0.052 高于当前阈值 0.05; 样本值 0.051 高于当前阈值 0.05</t>
+  </si>
+  <si>
+    <t>样本值 102000.0 高于当前阈值 100000.0; 样本值 105000.0 高于当前阈值 100000.0; 参数表与导入数据阈值冲突，请人工裁决</t>
+  </si>
+  <si>
+    <t>样本值 155.0 高于当前阈值 150.0; 样本值 152.0 高于当前阈值 150.0; 样本值 160.0 高于当前阈值 150.0</t>
+  </si>
+  <si>
+    <t>样本值 0.26 高于当前阈值 0.25</t>
+  </si>
+  <si>
+    <t>样本值 3.2 高于当前阈值 3.0; 样本值 4.5 高于当前阈值 3.0; 样本值 5.2 超出当前阈值 3.0 的150%</t>
+  </si>
+  <si>
+    <t>样本值 0.018 高于当前阈值 0.015; 样本值 0.025 超出当前阈值 0.015 的150%</t>
+  </si>
+  <si>
+    <t>样本值 0.42 高于当前阈值 0.4</t>
+  </si>
+  <si>
+    <t>{'样本数量': 5, '样本均值': 0.05, 'P95分位': 0.05, '超出阈值样本数': 2}</t>
   </si>
   <si>
     <t>{'参数表来源': '阈值=100000.0, 备注=阿乔202402手动调过：春节期间活动拉高，恢复正常后回落', '导入数据来源': '阈值=95000.0'}</t>
   </si>
   <si>
-    <t>{'参数表来源': '阈值=150.0, 备注=2023年底校准：大促后均值稳定在140-160区间', '导入数据来源': '阈值=180.0'}</t>
-  </si>
-  <si>
-    <t>{'样本数量': 3, '样本均值': 0.24, 'P95分位': 0.26, 'P99分位': 0.26}</t>
+    <t>{'样本数量': 5, '样本均值': 152.0, 'P95分位': 159.0, '超出阈值样本数': 3}</t>
   </si>
   <si>
     <t>{'样本数量': 5, '样本均值': 3.72, 'P95分位': 5.06, 'P99分位': 5.17, '越界样本数': 3}</t>
@@ -594,25 +615,28 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="I2" t="s">
+        <v>44</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K2">
         <v>0.055</v>
       </c>
       <c r="L2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -626,25 +650,25 @@
         <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -658,22 +682,22 @@
         <v>0.08</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -683,29 +707,32 @@
       <c r="B5">
         <v>150</v>
       </c>
+      <c r="C5">
+        <v>159</v>
+      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="L5" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -716,31 +743,31 @@
         <v>0.25</v>
       </c>
       <c r="C6">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
+        <v>47</v>
       </c>
       <c r="K6">
         <v>0.22</v>
       </c>
       <c r="L6" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -754,28 +781,28 @@
         <v>5.17</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -789,25 +816,25 @@
         <v>0.015</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="L8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -824,22 +851,25 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="I9" t="s">
+        <v>50</v>
       </c>
       <c r="K9">
         <v>0.35</v>
       </c>
       <c r="L9" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
